--- a/assets/Tech days and quote rates.xlsx
+++ b/assets/Tech days and quote rates.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bthall\tools\Pearson Quote Pro\Commissioning Pro\Repo\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bthall\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E14EC55-1DFA-4649-97DA-2EE5479CF76F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16E63CE9-1F3B-412D-9998-EB170C57148E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instal days by Model" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Requirements and Assumptions" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Instal days by Model'!$A$1:$C$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Instal days by Model'!$A$1:$C$45</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="85">
   <si>
     <t>Item</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>RPC-OU</t>
+  </si>
+  <si>
+    <t>BE60</t>
   </si>
 </sst>
 </file>
@@ -299,7 +302,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,6 +314,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -321,6 +325,11 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -375,7 +384,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -390,6 +399,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -495,10 +510,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E712DE08-B825-40F2-9FC0-5FEEF4F41363}" name="Table1" displayName="Table1" ref="A1:E44" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
-  <autoFilter ref="A1:E44" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C44">
-    <sortCondition ref="A1:A44"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E712DE08-B825-40F2-9FC0-5FEEF4F41363}" name="Table1" displayName="Table1" ref="A1:E45" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
+  <autoFilter ref="A1:E45" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C45">
+    <sortCondition ref="A1:A45"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{57C00BD4-A5D0-49E5-8AD4-B0CFA769C572}" name="Item"/>
@@ -821,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="31.5703125" customWidth="1"/>
@@ -845,13 +860,13 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
+      <c r="A2" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="8">
+        <v>2</v>
+      </c>
+      <c r="C2" s="8">
         <v>0</v>
       </c>
       <c r="D2" t="b">
@@ -863,7 +878,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -880,7 +895,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -897,7 +912,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -914,7 +929,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -931,7 +946,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -948,7 +963,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B8">
         <v>3</v>
@@ -965,7 +980,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -982,10 +997,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -999,7 +1014,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -1016,7 +1031,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -1033,10 +1048,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1050,10 +1065,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1067,7 +1082,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -1084,24 +1099,24 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1110,15 +1125,15 @@
         <v>0</v>
       </c>
       <c r="D17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1135,10 +1150,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1152,10 +1167,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1169,10 +1184,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1186,10 +1201,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1203,10 +1218,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1220,30 +1235,30 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="b">
         <v>0</v>
@@ -1254,30 +1269,30 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D27" t="b">
         <v>1</v>
@@ -1288,10 +1303,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -1305,10 +1320,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="B29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -1322,7 +1337,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B30">
         <v>4</v>
@@ -1339,13 +1354,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
@@ -1356,7 +1371,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -1373,7 +1388,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -1407,10 +1422,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -1424,7 +1439,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36">
         <v>3</v>
@@ -1458,10 +1473,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -1475,10 +1490,10 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -1492,7 +1507,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40">
         <v>3</v>
@@ -1509,7 +1524,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41">
         <v>3</v>
@@ -1526,30 +1541,30 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" t="b">
         <v>0</v>
@@ -1560,18 +1575,35 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>44</v>
       </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" t="b">
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" t="b">
         <v>1</v>
       </c>
     </row>

--- a/assets/Tech days and quote rates.xlsx
+++ b/assets/Tech days and quote rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bthall\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16E63CE9-1F3B-412D-9998-EB170C57148E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFFCF3C-8E53-452A-B5F8-A747D59DFD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -400,10 +400,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
@@ -864,7 +864,7 @@
         <v>84</v>
       </c>
       <c r="B2" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="8">
         <v>0</v>
@@ -1017,7 +1017,7 @@
         <v>21</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11">
         <v>0</v>
